--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753344963_h_10.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753344963_h_10.xlsx
@@ -658,7 +658,7 @@
         <v>0.008445755456178603</v>
       </c>
       <c r="C2" t="n">
-        <v>63463800</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>63463800</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>43961829</v>
+        <v>4017617</v>
       </c>
       <c r="L2" t="n">
-        <v>23727620</v>
+        <v>1756106</v>
       </c>
       <c r="M2" t="n">
-        <v>5538583</v>
+        <v>323970</v>
       </c>
       <c r="N2" t="n">
-        <v>265075</v>
+        <v>8923</v>
       </c>
       <c r="O2" t="n">
-        <v>3268839</v>
+        <v>190736</v>
       </c>
       <c r="P2" t="n">
-        <v>1211103</v>
+        <v>2369</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999878406524658</v>
+        <v>0.9999896287918091</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8477106690406799</v>
+        <v>0.7353699207305908</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7180054187774658</v>
+        <v>0.5490478873252869</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6550632119178772</v>
+        <v>0.4328140914440155</v>
       </c>
       <c r="U2" t="n">
-        <v>0.227798119187355</v>
+        <v>0.0456104464828968</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6967135071754456</v>
+        <v>0.4157388508319855</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8189159631729126</v>
+        <v>0.497898280620575</v>
       </c>
       <c r="X2" t="n">
-        <v>63463800</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>63463800</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>48303112</v>
+        <v>4789433</v>
       </c>
       <c r="AG2" t="n">
-        <v>29981680</v>
+        <v>3027015</v>
       </c>
       <c r="AH2" t="n">
-        <v>8027267</v>
+        <v>807060</v>
       </c>
       <c r="AI2" t="n">
-        <v>591860</v>
+        <v>59367</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4598515</v>
+        <v>461241</v>
       </c>
       <c r="AK2" t="n">
-        <v>1801493</v>
+        <v>180417</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9560742974281311</v>
+        <v>0.9549785256385803</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.911531388759613</v>
+        <v>0.912082850933075</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580335974693298</v>
+        <v>0.8579939603805542</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.661676824092865</v>
+        <v>0.6605360507965088</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019646048545837</v>
+        <v>0.90191650390625</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314513206481934</v>
+        <v>0.9314922094345093</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002023579242838846</v>
       </c>
       <c r="C3" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>43961829</v>
+        <v>4017617</v>
       </c>
       <c r="E3" t="n">
-        <v>6272301</v>
+        <v>938704</v>
       </c>
       <c r="F3" t="n">
-        <v>180332</v>
+        <v>38913</v>
       </c>
       <c r="G3" t="n">
-        <v>20212</v>
+        <v>4926</v>
       </c>
       <c r="H3" t="n">
-        <v>10546</v>
+        <v>2725</v>
       </c>
       <c r="I3" t="n">
-        <v>597</v>
+        <v>88</v>
       </c>
       <c r="J3" t="n">
-        <v>100695430</v>
+        <v>10069554</v>
       </c>
       <c r="K3" t="n">
-        <v>105816494</v>
+        <v>9967231</v>
       </c>
       <c r="L3" t="n">
-        <v>121887726</v>
+        <v>11645264</v>
       </c>
       <c r="M3" t="n">
-        <v>151878072</v>
+        <v>15048926</v>
       </c>
       <c r="N3" t="n">
-        <v>162366087</v>
+        <v>16139310</v>
       </c>
       <c r="O3" t="n">
-        <v>157635460</v>
+        <v>15636010</v>
       </c>
       <c r="P3" t="n">
-        <v>161957580</v>
+        <v>16219806</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8714655041694641</v>
+        <v>0.8030431866645813</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7200373411178589</v>
+        <v>0.5276150703430176</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5913830399513245</v>
+        <v>0.3437260091304779</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2960580587387085</v>
+        <v>0.09916868805885315</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6407501697540283</v>
+        <v>0.3725763559341431</v>
       </c>
       <c r="W3" t="n">
-        <v>0.626018226146698</v>
+        <v>0.01222362648695707</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>48303112</v>
+        <v>4789433</v>
       </c>
       <c r="Z3" t="n">
-        <v>1988133</v>
+        <v>198166</v>
       </c>
       <c r="AA3" t="n">
-        <v>85525</v>
+        <v>8476</v>
       </c>
       <c r="AB3" t="n">
-        <v>68445</v>
+        <v>6874</v>
       </c>
       <c r="AC3" t="n">
-        <v>348</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>100696200</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>111494909</v>
+        <v>11187217</v>
       </c>
       <c r="AG3" t="n">
-        <v>128296811</v>
+        <v>12795836</v>
       </c>
       <c r="AH3" t="n">
-        <v>153466369</v>
+        <v>15339900</v>
       </c>
       <c r="AI3" t="n">
-        <v>162962027</v>
+        <v>16295512</v>
       </c>
       <c r="AJ3" t="n">
-        <v>158558602</v>
+        <v>15853902</v>
       </c>
       <c r="AK3" t="n">
-        <v>162092809</v>
+        <v>16208926</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575237631797791</v>
+        <v>0.957314133644104</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9098227620124817</v>
+        <v>0.9094545841217041</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8571126461029053</v>
+        <v>0.8562752604484558</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6610390543937683</v>
+        <v>0.6597946286201477</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013901948928833</v>
+        <v>0.900970458984375</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311903715133667</v>
+        <v>0.9309202432632446</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03194845442669837</v>
       </c>
       <c r="C4" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>7331204</v>
+        <v>1304075</v>
       </c>
       <c r="E4" t="n">
-        <v>23727620</v>
+        <v>1756106</v>
       </c>
       <c r="F4" t="n">
-        <v>1591954</v>
+        <v>206812</v>
       </c>
       <c r="G4" t="n">
-        <v>126211</v>
+        <v>29767</v>
       </c>
       <c r="H4" t="n">
-        <v>162930</v>
+        <v>31341</v>
       </c>
       <c r="I4" t="n">
-        <v>13361</v>
+        <v>276</v>
       </c>
       <c r="J4" t="n">
-        <v>770</v>
+        <v>66</v>
       </c>
       <c r="K4" t="n">
-        <v>7897643</v>
+        <v>1445779</v>
       </c>
       <c r="L4" t="n">
-        <v>9318954</v>
+        <v>1442351</v>
       </c>
       <c r="M4" t="n">
-        <v>2916453</v>
+        <v>424550</v>
       </c>
       <c r="N4" t="n">
-        <v>898565</v>
+        <v>186712</v>
       </c>
       <c r="O4" t="n">
-        <v>1422959</v>
+        <v>268052</v>
       </c>
       <c r="P4" t="n">
-        <v>267807</v>
+        <v>2389</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999939203262329</v>
+        <v>0.9999948143959045</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8594239354133606</v>
+        <v>0.7677181363105774</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7190199494361877</v>
+        <v>0.5381181240081787</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6215963959693909</v>
+        <v>0.3831597566604614</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2574808597564697</v>
+        <v>0.06248315423727036</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6675610542297363</v>
+        <v>0.3929759860038757</v>
       </c>
       <c r="W4" t="n">
-        <v>0.709591269493103</v>
+        <v>0.02386144548654556</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2072431</v>
+        <v>211003</v>
       </c>
       <c r="Z4" t="n">
-        <v>29981680</v>
+        <v>3027015</v>
       </c>
       <c r="AA4" t="n">
-        <v>831668</v>
+        <v>83549</v>
       </c>
       <c r="AB4" t="n">
-        <v>55444</v>
+        <v>5619</v>
       </c>
       <c r="AC4" t="n">
-        <v>11417</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>680</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2219228</v>
+        <v>225793</v>
       </c>
       <c r="AG4" t="n">
-        <v>2909869</v>
+        <v>291779</v>
       </c>
       <c r="AH4" t="n">
-        <v>1328156</v>
+        <v>133576</v>
       </c>
       <c r="AI4" t="n">
-        <v>302625</v>
+        <v>30510</v>
       </c>
       <c r="AJ4" t="n">
-        <v>499817</v>
+        <v>50160</v>
       </c>
       <c r="AK4" t="n">
-        <v>132578</v>
+        <v>13269</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9567984938621521</v>
+        <v>0.9561448693275452</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106762409210205</v>
+        <v>0.9107667803764343</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8575728535652161</v>
+        <v>0.8571337461471558</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6613578200340271</v>
+        <v>0.6601651310920715</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016773700714111</v>
+        <v>0.9014432430267334</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.93132084608078</v>
+        <v>0.9312061071395874</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>402492</v>
+        <v>105472</v>
       </c>
       <c r="E5" t="n">
-        <v>2499106</v>
+        <v>383874</v>
       </c>
       <c r="F5" t="n">
-        <v>5538583</v>
+        <v>323970</v>
       </c>
       <c r="G5" t="n">
-        <v>282927</v>
+        <v>50196</v>
       </c>
       <c r="H5" t="n">
-        <v>589581</v>
+        <v>78438</v>
       </c>
       <c r="I5" t="n">
-        <v>52717</v>
+        <v>562</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6484034</v>
+        <v>985373</v>
       </c>
       <c r="L5" t="n">
-        <v>9225700</v>
+        <v>1572279</v>
       </c>
       <c r="M5" t="n">
-        <v>3826892</v>
+        <v>618554</v>
       </c>
       <c r="N5" t="n">
-        <v>630273</v>
+        <v>81055</v>
       </c>
       <c r="O5" t="n">
-        <v>1832742</v>
+        <v>321202</v>
       </c>
       <c r="P5" t="n">
-        <v>723510</v>
+        <v>191436</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999952912330627</v>
+        <v>0.9999960064888</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9123923182487488</v>
+        <v>0.85190349817276</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8870330452919006</v>
+        <v>0.8163602352142334</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9589221477508545</v>
+        <v>0.9364581108093262</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9906868934631348</v>
+        <v>0.9836886525154114</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9801675081253052</v>
+        <v>0.9641048908233643</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9939612746238708</v>
+        <v>0.9881929159164429</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>80954</v>
+        <v>8141</v>
       </c>
       <c r="Z5" t="n">
-        <v>859027</v>
+        <v>87332</v>
       </c>
       <c r="AA5" t="n">
-        <v>8027267</v>
+        <v>807060</v>
       </c>
       <c r="AB5" t="n">
-        <v>99883</v>
+        <v>10049</v>
       </c>
       <c r="AC5" t="n">
-        <v>292014</v>
+        <v>29309</v>
       </c>
       <c r="AD5" t="n">
-        <v>6330</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2142751</v>
+        <v>213557</v>
       </c>
       <c r="AG5" t="n">
-        <v>2971640</v>
+        <v>301370</v>
       </c>
       <c r="AH5" t="n">
-        <v>1338208</v>
+        <v>135464</v>
       </c>
       <c r="AI5" t="n">
-        <v>303488</v>
+        <v>30611</v>
       </c>
       <c r="AJ5" t="n">
-        <v>503066</v>
+        <v>50697</v>
       </c>
       <c r="AK5" t="n">
-        <v>133120</v>
+        <v>13388</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.97342848777771</v>
+        <v>0.9732365012168884</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641720652580261</v>
+        <v>0.9638676047325134</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837575554847717</v>
+        <v>0.9836111068725586</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963077902793884</v>
+        <v>0.9962767362594604</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938908219337463</v>
+        <v>0.9938561916351318</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998381495475769</v>
+        <v>0.9983761310577393</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>115</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>130568</v>
+        <v>21788</v>
       </c>
       <c r="E6" t="n">
-        <v>180604</v>
+        <v>25689</v>
       </c>
       <c r="F6" t="n">
-        <v>226535</v>
+        <v>24946</v>
       </c>
       <c r="G6" t="n">
-        <v>265075</v>
+        <v>8923</v>
       </c>
       <c r="H6" t="n">
-        <v>84004</v>
+        <v>8452</v>
       </c>
       <c r="I6" t="n">
-        <v>8447</v>
+        <v>173</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>65324</v>
+        <v>6613</v>
       </c>
       <c r="Z6" t="n">
-        <v>53793</v>
+        <v>5390</v>
       </c>
       <c r="AA6" t="n">
-        <v>109579</v>
+        <v>11097</v>
       </c>
       <c r="AB6" t="n">
-        <v>591860</v>
+        <v>59367</v>
       </c>
       <c r="AC6" t="n">
-        <v>69982</v>
+        <v>7030</v>
       </c>
       <c r="AD6" t="n">
-        <v>4810</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>186</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>31916</v>
+        <v>13538</v>
       </c>
       <c r="E7" t="n">
-        <v>335867</v>
+        <v>84447</v>
       </c>
       <c r="F7" t="n">
-        <v>852212</v>
+        <v>136238</v>
       </c>
       <c r="G7" t="n">
-        <v>419876</v>
+        <v>85676</v>
       </c>
       <c r="H7" t="n">
-        <v>3268839</v>
+        <v>190736</v>
       </c>
       <c r="I7" t="n">
-        <v>192685</v>
+        <v>1290</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>239</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8106</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>298070</v>
+        <v>30121</v>
       </c>
       <c r="AB7" t="n">
-        <v>76193</v>
+        <v>7701</v>
       </c>
       <c r="AC7" t="n">
-        <v>4598515</v>
+        <v>461241</v>
       </c>
       <c r="AD7" t="n">
-        <v>120458</v>
+        <v>12057</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>314</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>1463</v>
+        <v>906</v>
       </c>
       <c r="E8" t="n">
-        <v>31076</v>
+        <v>9637</v>
       </c>
       <c r="F8" t="n">
-        <v>65420</v>
+        <v>17641</v>
       </c>
       <c r="G8" t="n">
-        <v>49339</v>
+        <v>16147</v>
       </c>
       <c r="H8" t="n">
-        <v>575898</v>
+        <v>147096</v>
       </c>
       <c r="I8" t="n">
-        <v>1211103</v>
+        <v>2369</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>280</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>810</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3314</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2660</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>126056</v>
+        <v>12679</v>
       </c>
       <c r="AD8" t="n">
-        <v>1801493</v>
+        <v>180417</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
